--- a/Obiettivi.xlsx
+++ b/Obiettivi.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3611AF9-7A2E-46A7-AC25-F81286C632B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBDCB6DD-88BA-4BCA-ADAA-2AA61CFEED57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11,7 +11,6 @@
     <sheet name="Obiettivi" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -6309,7 +6308,239 @@
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">
-Presidia la Persia: tieni 2 sue province con almeno 6 uomini ciascuna</t>
+Costruisci una città in Arabia</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="8"/>
+        <color rgb="FF7A7A7A"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">
+[espansione] 4 province persiane con soldati ≥ 7 ciascuna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Il tesoro per i Safavidi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">
+Costruisci 1 nave e  conquista 1 provincia in africa centrale</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="8"/>
+        <color rgb="FF7A7A7A"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">
+[economia] monete ≥ 2000</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Isfahan è metà del mondo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">
+Espandi il tuo dominio ad almeno 15 province</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="8"/>
+        <color rgb="FF7A7A7A"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">
+[crescita] una Città a Isfahan con soldati ≥ 6 e Città ≥ 3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Il regno che si governa</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">
+Sbarca in Turchia per combattere i cristiani</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="8"/>
+        <color rgb="FF7A7A7A"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">
+[crescita] Popolarità ≥ 4</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>La dinastia non cede</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">
+Conquista Hudavendigar e presidiala con 8 uomini</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="8"/>
+        <color rgb="FF7A7A7A"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">
+[espansione] province di PERSIA ≥ 6 e Fortezze ≥ 2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>La pace armata</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">
+Ogni provincia confinante con nemici con almeno 5 uomini</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="8"/>
+        <color rgb="FF7A7A7A"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">
+[crescita] Sicurezza ≥ 4</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Ogni confine armato</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">
+Conserva 3 risorse per ogni tipo</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="8"/>
+        <color rgb="FF7A7A7A"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">
+[espansione] ogni provincia di confine con soldati ≥ 5</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Sbocco al mare</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">
+Conquista 3 province che sboccano sul mare e difendile con almeno 3 uomini ciascuna</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="8"/>
+        <color rgb="FF7A7A7A"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">
+[espansione] 3 province costiere</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1A1A1A"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>La Persia presidiata</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">
+Presidia la Persia: tieni 3 sue province con almeno 6 uomini ciascuna</t>
     </r>
     <r>
       <rPr>
@@ -6320,238 +6551,6 @@
       </rPr>
       <t xml:space="preserve">
 [espansione] 2 province persiane con soldati ≥ 5 ciascuna</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1A1A1A"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>La Persia presidiata</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">
-Costruisci una città in Arabia</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="8"/>
-        <color rgb="FF7A7A7A"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">
-[espansione] 4 province persiane con soldati ≥ 7 ciascuna</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1A1A1A"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>Il tesoro per i Safavidi</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">
-Costruisci 1 nave e  conquista 1 provincia in africa centrale</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="8"/>
-        <color rgb="FF7A7A7A"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">
-[economia] monete ≥ 2000</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1A1A1A"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>Isfahan è metà del mondo</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">
-Espandi il tuo dominio ad almeno 15 province</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="8"/>
-        <color rgb="FF7A7A7A"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">
-[crescita] una Città a Isfahan con soldati ≥ 6 e Città ≥ 3</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1A1A1A"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>Il regno che si governa</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">
-Sbarca in Turchia per combattere i cristiani</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="8"/>
-        <color rgb="FF7A7A7A"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">
-[crescita] Popolarità ≥ 4</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1A1A1A"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>La dinastia non cede</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">
-Conquista Hudavendigar e presidiala con 8 uomini</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="8"/>
-        <color rgb="FF7A7A7A"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">
-[espansione] province di PERSIA ≥ 6 e Fortezze ≥ 2</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1A1A1A"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>La pace armata</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">
-Ogni provincia confinante con nemici con almeno 5 uomini</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="8"/>
-        <color rgb="FF7A7A7A"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">
-[crescita] Sicurezza ≥ 4</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1A1A1A"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>Ogni confine armato</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">
-Conserva 3 risorse per ogni tipo</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="8"/>
-        <color rgb="FF7A7A7A"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">
-[espansione] ogni provincia di confine con soldati ≥ 5</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1A1A1A"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>Sbocco al mare</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">
-Conquista 3 province che sboccano sul mare e difendile con almeno 3 uomini ciascuna</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="8"/>
-        <color rgb="FF7A7A7A"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">
-[espansione] 3 province costiere</t>
     </r>
   </si>
 </sst>
@@ -6747,7 +6746,19 @@
     <xf numFmtId="0" fontId="10" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6765,19 +6776,7 @@
     <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -7150,108 +7149,108 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:40" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="F1" s="13" t="s">
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="F1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="J1" s="14" t="s">
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="J1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-      <c r="N1" s="15" t="s">
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+      <c r="N1" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="O1" s="15"/>
-      <c r="P1" s="15"/>
-      <c r="R1" s="16" t="s">
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="R1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="S1" s="16"/>
-      <c r="T1" s="16"/>
-      <c r="V1" s="7" t="s">
+      <c r="S1" s="10"/>
+      <c r="T1" s="10"/>
+      <c r="V1" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="W1" s="7"/>
-      <c r="X1" s="7"/>
-      <c r="Z1" s="8" t="s">
+      <c r="W1" s="11"/>
+      <c r="X1" s="11"/>
+      <c r="Z1" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="AA1" s="8"/>
-      <c r="AB1" s="8"/>
-      <c r="AD1" s="9" t="s">
+      <c r="AA1" s="12"/>
+      <c r="AB1" s="12"/>
+      <c r="AD1" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="AE1" s="9"/>
-      <c r="AF1" s="9"/>
-      <c r="AH1" s="10" t="s">
+      <c r="AE1" s="13"/>
+      <c r="AF1" s="13"/>
+      <c r="AH1" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="AI1" s="10"/>
-      <c r="AJ1" s="10"/>
-      <c r="AL1" s="11" t="s">
+      <c r="AI1" s="14"/>
+      <c r="AJ1" s="14"/>
+      <c r="AL1" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="AM1" s="11"/>
-      <c r="AN1" s="11"/>
+      <c r="AM1" s="15"/>
+      <c r="AN1" s="15"/>
     </row>
     <row r="2" spans="2:40" ht="12" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="F2" s="6" t="s">
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="F2" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="J2" s="6" t="s">
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="J2" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="N2" s="6" t="s">
+      <c r="K2" s="16"/>
+      <c r="L2" s="16"/>
+      <c r="N2" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="O2" s="6"/>
-      <c r="P2" s="6"/>
-      <c r="R2" s="6" t="s">
+      <c r="O2" s="16"/>
+      <c r="P2" s="16"/>
+      <c r="R2" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="S2" s="6"/>
-      <c r="T2" s="6"/>
-      <c r="V2" s="6" t="s">
+      <c r="S2" s="16"/>
+      <c r="T2" s="16"/>
+      <c r="V2" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="W2" s="6"/>
-      <c r="X2" s="6"/>
-      <c r="Z2" s="6" t="s">
+      <c r="W2" s="16"/>
+      <c r="X2" s="16"/>
+      <c r="Z2" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="AA2" s="6"/>
-      <c r="AB2" s="6"/>
-      <c r="AD2" s="6" t="s">
+      <c r="AA2" s="16"/>
+      <c r="AB2" s="16"/>
+      <c r="AD2" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="AE2" s="6"/>
-      <c r="AF2" s="6"/>
-      <c r="AH2" s="6" t="s">
+      <c r="AE2" s="16"/>
+      <c r="AF2" s="16"/>
+      <c r="AH2" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="AI2" s="6"/>
-      <c r="AJ2" s="6"/>
-      <c r="AL2" s="6" t="s">
+      <c r="AI2" s="16"/>
+      <c r="AJ2" s="16"/>
+      <c r="AL2" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="AM2" s="6"/>
-      <c r="AN2" s="6"/>
+      <c r="AM2" s="16"/>
+      <c r="AN2" s="16"/>
     </row>
     <row r="3" spans="2:40" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="1" t="s">
@@ -7383,7 +7382,7 @@
         <v>23</v>
       </c>
       <c r="R4" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="S4" s="2" t="s">
         <v>24</v>
@@ -7438,56 +7437,56 @@
       </c>
     </row>
     <row r="5" spans="2:40" ht="12" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="F5" s="6" t="s">
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="F5" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-      <c r="J5" s="6" t="s">
+      <c r="G5" s="16"/>
+      <c r="H5" s="16"/>
+      <c r="J5" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="K5" s="6"/>
-      <c r="L5" s="6"/>
-      <c r="N5" s="6" t="s">
+      <c r="K5" s="16"/>
+      <c r="L5" s="16"/>
+      <c r="N5" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="O5" s="6"/>
-      <c r="P5" s="6"/>
-      <c r="R5" s="6" t="s">
+      <c r="O5" s="16"/>
+      <c r="P5" s="16"/>
+      <c r="R5" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="S5" s="6"/>
-      <c r="T5" s="6"/>
-      <c r="V5" s="6" t="s">
+      <c r="S5" s="16"/>
+      <c r="T5" s="16"/>
+      <c r="V5" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="W5" s="6"/>
-      <c r="X5" s="6"/>
-      <c r="Z5" s="6" t="s">
+      <c r="W5" s="16"/>
+      <c r="X5" s="16"/>
+      <c r="Z5" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="AA5" s="6"/>
-      <c r="AB5" s="6"/>
-      <c r="AD5" s="6" t="s">
+      <c r="AA5" s="16"/>
+      <c r="AB5" s="16"/>
+      <c r="AD5" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="AE5" s="6"/>
-      <c r="AF5" s="6"/>
-      <c r="AH5" s="6" t="s">
+      <c r="AE5" s="16"/>
+      <c r="AF5" s="16"/>
+      <c r="AH5" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="AI5" s="6"/>
-      <c r="AJ5" s="6"/>
-      <c r="AL5" s="6" t="s">
+      <c r="AI5" s="16"/>
+      <c r="AJ5" s="16"/>
+      <c r="AL5" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="AM5" s="6"/>
-      <c r="AN5" s="6"/>
+      <c r="AM5" s="16"/>
+      <c r="AN5" s="16"/>
     </row>
     <row r="6" spans="2:40" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B6" s="1" t="s">
@@ -7674,56 +7673,56 @@
       </c>
     </row>
     <row r="8" spans="2:40" ht="12" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="F8" s="6" t="s">
+      <c r="C8" s="16"/>
+      <c r="D8" s="16"/>
+      <c r="F8" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="J8" s="6" t="s">
+      <c r="G8" s="16"/>
+      <c r="H8" s="16"/>
+      <c r="J8" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="K8" s="6"/>
-      <c r="L8" s="6"/>
-      <c r="N8" s="6" t="s">
+      <c r="K8" s="16"/>
+      <c r="L8" s="16"/>
+      <c r="N8" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="O8" s="6"/>
-      <c r="P8" s="6"/>
-      <c r="R8" s="6" t="s">
+      <c r="O8" s="16"/>
+      <c r="P8" s="16"/>
+      <c r="R8" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="S8" s="6"/>
-      <c r="T8" s="6"/>
-      <c r="V8" s="6" t="s">
+      <c r="S8" s="16"/>
+      <c r="T8" s="16"/>
+      <c r="V8" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="W8" s="6"/>
-      <c r="X8" s="6"/>
-      <c r="Z8" s="6" t="s">
+      <c r="W8" s="16"/>
+      <c r="X8" s="16"/>
+      <c r="Z8" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="AA8" s="6"/>
-      <c r="AB8" s="6"/>
-      <c r="AD8" s="6" t="s">
+      <c r="AA8" s="16"/>
+      <c r="AB8" s="16"/>
+      <c r="AD8" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="AE8" s="6"/>
-      <c r="AF8" s="6"/>
-      <c r="AH8" s="6" t="s">
+      <c r="AE8" s="16"/>
+      <c r="AF8" s="16"/>
+      <c r="AH8" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="AI8" s="6"/>
-      <c r="AJ8" s="6"/>
-      <c r="AL8" s="6" t="s">
+      <c r="AI8" s="16"/>
+      <c r="AJ8" s="16"/>
+      <c r="AL8" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="AM8" s="6"/>
-      <c r="AN8" s="6"/>
+      <c r="AM8" s="16"/>
+      <c r="AN8" s="16"/>
     </row>
     <row r="9" spans="2:40" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="1" t="s">
@@ -7910,56 +7909,56 @@
       </c>
     </row>
     <row r="11" spans="2:40" ht="12" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="F11" s="6" t="s">
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
+      <c r="F11" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-      <c r="J11" s="6" t="s">
+      <c r="G11" s="16"/>
+      <c r="H11" s="16"/>
+      <c r="J11" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="K11" s="6"/>
-      <c r="L11" s="6"/>
-      <c r="N11" s="6" t="s">
+      <c r="K11" s="16"/>
+      <c r="L11" s="16"/>
+      <c r="N11" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="O11" s="6"/>
-      <c r="P11" s="6"/>
-      <c r="R11" s="6" t="s">
+      <c r="O11" s="16"/>
+      <c r="P11" s="16"/>
+      <c r="R11" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="S11" s="6"/>
-      <c r="T11" s="6"/>
-      <c r="V11" s="6" t="s">
+      <c r="S11" s="16"/>
+      <c r="T11" s="16"/>
+      <c r="V11" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="W11" s="6"/>
-      <c r="X11" s="6"/>
-      <c r="Z11" s="6" t="s">
+      <c r="W11" s="16"/>
+      <c r="X11" s="16"/>
+      <c r="Z11" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="AA11" s="6"/>
-      <c r="AB11" s="6"/>
-      <c r="AD11" s="6" t="s">
+      <c r="AA11" s="16"/>
+      <c r="AB11" s="16"/>
+      <c r="AD11" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="AE11" s="6"/>
-      <c r="AF11" s="6"/>
-      <c r="AH11" s="6" t="s">
+      <c r="AE11" s="16"/>
+      <c r="AF11" s="16"/>
+      <c r="AH11" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="AI11" s="6"/>
-      <c r="AJ11" s="6"/>
-      <c r="AL11" s="6" t="s">
+      <c r="AI11" s="16"/>
+      <c r="AJ11" s="16"/>
+      <c r="AL11" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="AM11" s="6"/>
-      <c r="AN11" s="6"/>
+      <c r="AM11" s="16"/>
+      <c r="AN11" s="16"/>
     </row>
     <row r="12" spans="2:40" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="1" t="s">
@@ -8138,64 +8137,64 @@
       <c r="AL13" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="AM13" s="3" t="s">
-        <v>235</v>
+      <c r="AM13" s="4" t="s">
+        <v>243</v>
       </c>
       <c r="AN13" s="3" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="14" spans="2:40" ht="12" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="F14" s="6" t="s">
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="F14" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="J14" s="6" t="s">
+      <c r="G14" s="16"/>
+      <c r="H14" s="16"/>
+      <c r="J14" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="K14" s="6"/>
-      <c r="L14" s="6"/>
-      <c r="N14" s="6" t="s">
+      <c r="K14" s="16"/>
+      <c r="L14" s="16"/>
+      <c r="N14" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="O14" s="6"/>
-      <c r="P14" s="6"/>
-      <c r="R14" s="6" t="s">
+      <c r="O14" s="16"/>
+      <c r="P14" s="16"/>
+      <c r="R14" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="S14" s="6"/>
-      <c r="T14" s="6"/>
-      <c r="V14" s="6" t="s">
+      <c r="S14" s="16"/>
+      <c r="T14" s="16"/>
+      <c r="V14" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="W14" s="6"/>
-      <c r="X14" s="6"/>
-      <c r="Z14" s="6" t="s">
+      <c r="W14" s="16"/>
+      <c r="X14" s="16"/>
+      <c r="Z14" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="AA14" s="6"/>
-      <c r="AB14" s="6"/>
-      <c r="AD14" s="6" t="s">
+      <c r="AA14" s="16"/>
+      <c r="AB14" s="16"/>
+      <c r="AD14" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="AE14" s="6"/>
-      <c r="AF14" s="6"/>
-      <c r="AH14" s="6" t="s">
+      <c r="AE14" s="16"/>
+      <c r="AF14" s="16"/>
+      <c r="AH14" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="AI14" s="6"/>
-      <c r="AJ14" s="6"/>
-      <c r="AL14" s="6" t="s">
+      <c r="AI14" s="16"/>
+      <c r="AJ14" s="16"/>
+      <c r="AL14" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="AM14" s="6"/>
-      <c r="AN14" s="6"/>
+      <c r="AM14" s="16"/>
+      <c r="AN14" s="16"/>
     </row>
     <row r="15" spans="2:40" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="2" t="s">
@@ -8372,66 +8371,66 @@
         <v>227</v>
       </c>
       <c r="AL16" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="AM16" s="3" t="s">
         <v>236</v>
-      </c>
-      <c r="AM16" s="3" t="s">
-        <v>237</v>
       </c>
       <c r="AN16" s="4" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="17" spans="2:40" ht="12" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="F17" s="6" t="s">
+      <c r="C17" s="16"/>
+      <c r="D17" s="16"/>
+      <c r="F17" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
-      <c r="J17" s="6" t="s">
+      <c r="G17" s="16"/>
+      <c r="H17" s="16"/>
+      <c r="J17" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="K17" s="6"/>
-      <c r="L17" s="6"/>
-      <c r="N17" s="6" t="s">
+      <c r="K17" s="16"/>
+      <c r="L17" s="16"/>
+      <c r="N17" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="O17" s="6"/>
-      <c r="P17" s="6"/>
-      <c r="R17" s="6" t="s">
+      <c r="O17" s="16"/>
+      <c r="P17" s="16"/>
+      <c r="R17" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="S17" s="6"/>
-      <c r="T17" s="6"/>
-      <c r="V17" s="6" t="s">
+      <c r="S17" s="16"/>
+      <c r="T17" s="16"/>
+      <c r="V17" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="W17" s="6"/>
-      <c r="X17" s="6"/>
-      <c r="Z17" s="6" t="s">
+      <c r="W17" s="16"/>
+      <c r="X17" s="16"/>
+      <c r="Z17" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="AA17" s="6"/>
-      <c r="AB17" s="6"/>
-      <c r="AD17" s="6" t="s">
+      <c r="AA17" s="16"/>
+      <c r="AB17" s="16"/>
+      <c r="AD17" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="AE17" s="6"/>
-      <c r="AF17" s="6"/>
-      <c r="AH17" s="6" t="s">
+      <c r="AE17" s="16"/>
+      <c r="AF17" s="16"/>
+      <c r="AH17" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="AI17" s="6"/>
-      <c r="AJ17" s="6"/>
-      <c r="AL17" s="6" t="s">
+      <c r="AI17" s="16"/>
+      <c r="AJ17" s="16"/>
+      <c r="AL17" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="AM17" s="6"/>
-      <c r="AN17" s="6"/>
+      <c r="AM17" s="16"/>
+      <c r="AN17" s="16"/>
     </row>
     <row r="18" spans="2:40" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B18" s="2" t="s">
@@ -8618,56 +8617,56 @@
       </c>
     </row>
     <row r="20" spans="2:40" ht="12" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
-      <c r="F20" s="6" t="s">
+      <c r="C20" s="16"/>
+      <c r="D20" s="16"/>
+      <c r="F20" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
-      <c r="J20" s="6" t="s">
+      <c r="G20" s="16"/>
+      <c r="H20" s="16"/>
+      <c r="J20" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="K20" s="6"/>
-      <c r="L20" s="6"/>
-      <c r="N20" s="6" t="s">
+      <c r="K20" s="16"/>
+      <c r="L20" s="16"/>
+      <c r="N20" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="O20" s="6"/>
-      <c r="P20" s="6"/>
-      <c r="R20" s="6" t="s">
+      <c r="O20" s="16"/>
+      <c r="P20" s="16"/>
+      <c r="R20" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="S20" s="6"/>
-      <c r="T20" s="6"/>
-      <c r="V20" s="6" t="s">
+      <c r="S20" s="16"/>
+      <c r="T20" s="16"/>
+      <c r="V20" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="W20" s="6"/>
-      <c r="X20" s="6"/>
-      <c r="Z20" s="6" t="s">
+      <c r="W20" s="16"/>
+      <c r="X20" s="16"/>
+      <c r="Z20" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="AA20" s="6"/>
-      <c r="AB20" s="6"/>
-      <c r="AD20" s="6" t="s">
+      <c r="AA20" s="16"/>
+      <c r="AB20" s="16"/>
+      <c r="AD20" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="AE20" s="6"/>
-      <c r="AF20" s="6"/>
-      <c r="AH20" s="6" t="s">
+      <c r="AE20" s="16"/>
+      <c r="AF20" s="16"/>
+      <c r="AH20" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="AI20" s="6"/>
-      <c r="AJ20" s="6"/>
-      <c r="AL20" s="6" t="s">
+      <c r="AI20" s="16"/>
+      <c r="AJ20" s="16"/>
+      <c r="AL20" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="AM20" s="6"/>
-      <c r="AN20" s="6"/>
+      <c r="AM20" s="16"/>
+      <c r="AN20" s="16"/>
     </row>
     <row r="21" spans="2:40" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B21" s="2" t="s">
@@ -8844,66 +8843,66 @@
         <v>229</v>
       </c>
       <c r="AL22" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="AM22" s="4" t="s">
         <v>73</v>
       </c>
       <c r="AN22" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="23" spans="2:40" ht="12" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="16" t="s">
         <v>117</v>
       </c>
-      <c r="C23" s="6"/>
-      <c r="D23" s="6"/>
-      <c r="F23" s="6" t="s">
+      <c r="C23" s="16"/>
+      <c r="D23" s="16"/>
+      <c r="F23" s="16" t="s">
         <v>117</v>
       </c>
-      <c r="G23" s="6"/>
-      <c r="H23" s="6"/>
-      <c r="J23" s="6" t="s">
+      <c r="G23" s="16"/>
+      <c r="H23" s="16"/>
+      <c r="J23" s="16" t="s">
         <v>117</v>
       </c>
-      <c r="K23" s="6"/>
-      <c r="L23" s="6"/>
-      <c r="N23" s="6" t="s">
+      <c r="K23" s="16"/>
+      <c r="L23" s="16"/>
+      <c r="N23" s="16" t="s">
         <v>117</v>
       </c>
-      <c r="O23" s="6"/>
-      <c r="P23" s="6"/>
-      <c r="R23" s="6" t="s">
+      <c r="O23" s="16"/>
+      <c r="P23" s="16"/>
+      <c r="R23" s="16" t="s">
         <v>117</v>
       </c>
-      <c r="S23" s="6"/>
-      <c r="T23" s="6"/>
-      <c r="V23" s="6" t="s">
+      <c r="S23" s="16"/>
+      <c r="T23" s="16"/>
+      <c r="V23" s="16" t="s">
         <v>117</v>
       </c>
-      <c r="W23" s="6"/>
-      <c r="X23" s="6"/>
-      <c r="Z23" s="6" t="s">
+      <c r="W23" s="16"/>
+      <c r="X23" s="16"/>
+      <c r="Z23" s="16" t="s">
         <v>117</v>
       </c>
-      <c r="AA23" s="6"/>
-      <c r="AB23" s="6"/>
-      <c r="AD23" s="6" t="s">
+      <c r="AA23" s="16"/>
+      <c r="AB23" s="16"/>
+      <c r="AD23" s="16" t="s">
         <v>117</v>
       </c>
-      <c r="AE23" s="6"/>
-      <c r="AF23" s="6"/>
-      <c r="AH23" s="6" t="s">
+      <c r="AE23" s="16"/>
+      <c r="AF23" s="16"/>
+      <c r="AH23" s="16" t="s">
         <v>117</v>
       </c>
-      <c r="AI23" s="6"/>
-      <c r="AJ23" s="6"/>
-      <c r="AL23" s="6" t="s">
+      <c r="AI23" s="16"/>
+      <c r="AJ23" s="16"/>
+      <c r="AL23" s="16" t="s">
         <v>117</v>
       </c>
-      <c r="AM23" s="6"/>
-      <c r="AN23" s="6"/>
+      <c r="AM23" s="16"/>
+      <c r="AN23" s="16"/>
     </row>
     <row r="24" spans="2:40" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="2" t="s">
@@ -9077,13 +9076,13 @@
         <v>230</v>
       </c>
       <c r="AL25" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="AM25" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="AM25" s="3" t="s">
+      <c r="AN25" s="3" t="s">
         <v>241</v>
-      </c>
-      <c r="AN25" s="3" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="26" spans="2:40" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
@@ -9136,96 +9135,96 @@
     </row>
   </sheetData>
   <mergeCells count="90">
+    <mergeCell ref="V23:X23"/>
+    <mergeCell ref="Z23:AB23"/>
+    <mergeCell ref="AD23:AF23"/>
+    <mergeCell ref="AH23:AJ23"/>
+    <mergeCell ref="AL23:AN23"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="J23:L23"/>
+    <mergeCell ref="N23:P23"/>
+    <mergeCell ref="R23:T23"/>
+    <mergeCell ref="V20:X20"/>
+    <mergeCell ref="Z20:AB20"/>
+    <mergeCell ref="AD20:AF20"/>
+    <mergeCell ref="AH20:AJ20"/>
+    <mergeCell ref="AL20:AN20"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="J20:L20"/>
+    <mergeCell ref="N20:P20"/>
+    <mergeCell ref="R20:T20"/>
+    <mergeCell ref="V17:X17"/>
+    <mergeCell ref="Z17:AB17"/>
+    <mergeCell ref="AD17:AF17"/>
+    <mergeCell ref="AH17:AJ17"/>
+    <mergeCell ref="AL17:AN17"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="J17:L17"/>
+    <mergeCell ref="N17:P17"/>
+    <mergeCell ref="R17:T17"/>
+    <mergeCell ref="V14:X14"/>
+    <mergeCell ref="Z14:AB14"/>
+    <mergeCell ref="AD14:AF14"/>
+    <mergeCell ref="AH14:AJ14"/>
+    <mergeCell ref="AL14:AN14"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="J14:L14"/>
+    <mergeCell ref="N14:P14"/>
+    <mergeCell ref="R14:T14"/>
+    <mergeCell ref="V11:X11"/>
+    <mergeCell ref="Z11:AB11"/>
+    <mergeCell ref="AD11:AF11"/>
+    <mergeCell ref="AH11:AJ11"/>
+    <mergeCell ref="AL11:AN11"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="F11:H11"/>
+    <mergeCell ref="J11:L11"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="R11:T11"/>
+    <mergeCell ref="V8:X8"/>
+    <mergeCell ref="Z8:AB8"/>
+    <mergeCell ref="AD8:AF8"/>
+    <mergeCell ref="AH8:AJ8"/>
+    <mergeCell ref="AL8:AN8"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="J8:L8"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="R8:T8"/>
+    <mergeCell ref="V5:X5"/>
+    <mergeCell ref="Z5:AB5"/>
+    <mergeCell ref="AD5:AF5"/>
+    <mergeCell ref="AH5:AJ5"/>
+    <mergeCell ref="AL5:AN5"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="F5:H5"/>
+    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="N5:P5"/>
+    <mergeCell ref="R5:T5"/>
+    <mergeCell ref="V2:X2"/>
+    <mergeCell ref="Z2:AB2"/>
+    <mergeCell ref="AD2:AF2"/>
+    <mergeCell ref="AH2:AJ2"/>
+    <mergeCell ref="AL2:AN2"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="J2:L2"/>
+    <mergeCell ref="N2:P2"/>
+    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="V1:X1"/>
+    <mergeCell ref="Z1:AB1"/>
+    <mergeCell ref="AD1:AF1"/>
+    <mergeCell ref="AH1:AJ1"/>
+    <mergeCell ref="AL1:AN1"/>
     <mergeCell ref="B1:D1"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="J1:L1"/>
     <mergeCell ref="N1:P1"/>
     <mergeCell ref="R1:T1"/>
-    <mergeCell ref="V1:X1"/>
-    <mergeCell ref="Z1:AB1"/>
-    <mergeCell ref="AD1:AF1"/>
-    <mergeCell ref="AH1:AJ1"/>
-    <mergeCell ref="AL1:AN1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="J2:L2"/>
-    <mergeCell ref="N2:P2"/>
-    <mergeCell ref="R2:T2"/>
-    <mergeCell ref="V2:X2"/>
-    <mergeCell ref="Z2:AB2"/>
-    <mergeCell ref="AD2:AF2"/>
-    <mergeCell ref="AH2:AJ2"/>
-    <mergeCell ref="AL2:AN2"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="F5:H5"/>
-    <mergeCell ref="J5:L5"/>
-    <mergeCell ref="N5:P5"/>
-    <mergeCell ref="R5:T5"/>
-    <mergeCell ref="V5:X5"/>
-    <mergeCell ref="Z5:AB5"/>
-    <mergeCell ref="AD5:AF5"/>
-    <mergeCell ref="AH5:AJ5"/>
-    <mergeCell ref="AL5:AN5"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="J8:L8"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="R8:T8"/>
-    <mergeCell ref="V8:X8"/>
-    <mergeCell ref="Z8:AB8"/>
-    <mergeCell ref="AD8:AF8"/>
-    <mergeCell ref="AH8:AJ8"/>
-    <mergeCell ref="AL8:AN8"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="F11:H11"/>
-    <mergeCell ref="J11:L11"/>
-    <mergeCell ref="N11:P11"/>
-    <mergeCell ref="R11:T11"/>
-    <mergeCell ref="V11:X11"/>
-    <mergeCell ref="Z11:AB11"/>
-    <mergeCell ref="AD11:AF11"/>
-    <mergeCell ref="AH11:AJ11"/>
-    <mergeCell ref="AL11:AN11"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="J14:L14"/>
-    <mergeCell ref="N14:P14"/>
-    <mergeCell ref="R14:T14"/>
-    <mergeCell ref="V14:X14"/>
-    <mergeCell ref="Z14:AB14"/>
-    <mergeCell ref="AD14:AF14"/>
-    <mergeCell ref="AH14:AJ14"/>
-    <mergeCell ref="AL14:AN14"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="J17:L17"/>
-    <mergeCell ref="N17:P17"/>
-    <mergeCell ref="R17:T17"/>
-    <mergeCell ref="V17:X17"/>
-    <mergeCell ref="Z17:AB17"/>
-    <mergeCell ref="AD17:AF17"/>
-    <mergeCell ref="AH17:AJ17"/>
-    <mergeCell ref="AL17:AN17"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="F20:H20"/>
-    <mergeCell ref="J20:L20"/>
-    <mergeCell ref="N20:P20"/>
-    <mergeCell ref="R20:T20"/>
-    <mergeCell ref="V20:X20"/>
-    <mergeCell ref="Z20:AB20"/>
-    <mergeCell ref="AD20:AF20"/>
-    <mergeCell ref="AH20:AJ20"/>
-    <mergeCell ref="AL20:AN20"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="J23:L23"/>
-    <mergeCell ref="N23:P23"/>
-    <mergeCell ref="R23:T23"/>
-    <mergeCell ref="V23:X23"/>
-    <mergeCell ref="Z23:AB23"/>
-    <mergeCell ref="AD23:AF23"/>
-    <mergeCell ref="AH23:AJ23"/>
-    <mergeCell ref="AL23:AN23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
